--- a/Analysis/duplication_rates_all_runs.xlsx
+++ b/Analysis/duplication_rates_all_runs.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,16 +478,16 @@
         <v>210</v>
       </c>
       <c r="F2" t="n">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
-        <v>77.619</v>
+        <v>43.8095</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -507,16 +507,16 @@
         <v>180</v>
       </c>
       <c r="F3" t="n">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="G3" t="n">
-        <v>98.33329999999999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,16 +536,16 @@
         <v>195</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3333</v>
+        <v>6.1538</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,16 +565,16 @@
         <v>210</v>
       </c>
       <c r="F5" t="n">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
-        <v>73.8095</v>
+        <v>44.2857</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -594,16 +594,16 @@
         <v>180</v>
       </c>
       <c r="F6" t="n">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>96.66670000000001</v>
+        <v>61.1111</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -623,16 +623,16 @@
         <v>195</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>16.4103</v>
+        <v>7.1795</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -652,16 +652,16 @@
         <v>210</v>
       </c>
       <c r="F8" t="n">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>74.7619</v>
+        <v>42.8571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -681,16 +681,16 @@
         <v>180</v>
       </c>
       <c r="F9" t="n">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="G9" t="n">
-        <v>97.2222</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -710,16 +710,16 @@
         <v>195</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G10" t="n">
-        <v>17.9487</v>
+        <v>7.1795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -739,16 +739,16 @@
         <v>210</v>
       </c>
       <c r="F11" t="n">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="G11" t="n">
-        <v>78.09520000000001</v>
+        <v>39.5238</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -768,16 +768,16 @@
         <v>180</v>
       </c>
       <c r="F12" t="n">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="G12" t="n">
-        <v>95.5556</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -797,16 +797,16 @@
         <v>195</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>14.359</v>
+        <v>8.2051</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -826,16 +826,16 @@
         <v>210</v>
       </c>
       <c r="F14" t="n">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="G14" t="n">
-        <v>78.5714</v>
+        <v>44.7619</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -855,16 +855,16 @@
         <v>180</v>
       </c>
       <c r="F15" t="n">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G15" t="n">
-        <v>95</v>
+        <v>71.11109999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -884,16 +884,16 @@
         <v>195</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>13.3333</v>
+        <v>6.1538</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F17" t="n">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="G17" t="n">
-        <v>98.55070000000001</v>
+        <v>90.9524</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -942,16 +942,16 @@
         <v>180</v>
       </c>
       <c r="F18" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G18" t="n">
-        <v>66.11109999999999</v>
+        <v>67.7778</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -971,16 +971,16 @@
         <v>195</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>21.5385</v>
+        <v>21.0256</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F20" t="n">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>85.71429999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1029,16 +1029,16 @@
         <v>180</v>
       </c>
       <c r="F21" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G21" t="n">
-        <v>67.7778</v>
+        <v>66.66670000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" t="n">
-        <v>22.3958</v>
+        <v>22.5641</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1087,16 +1087,16 @@
         <v>210</v>
       </c>
       <c r="F23" t="n">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="G23" t="n">
-        <v>98.5714</v>
+        <v>93.33329999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1116,16 +1116,16 @@
         <v>180</v>
       </c>
       <c r="F24" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G24" t="n">
-        <v>66.11109999999999</v>
+        <v>66.66670000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G25" t="n">
-        <v>21.6931</v>
+        <v>23.0769</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1174,16 +1174,16 @@
         <v>210</v>
       </c>
       <c r="F26" t="n">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="G26" t="n">
-        <v>99.52379999999999</v>
+        <v>89.0476</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1203,16 +1203,16 @@
         <v>180</v>
       </c>
       <c r="F27" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G27" t="n">
-        <v>67.2222</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1229,19 +1229,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
-        <v>20.6349</v>
+        <v>21.0256</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F29" t="n">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="G29" t="n">
-        <v>98.55070000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1290,16 +1290,16 @@
         <v>180</v>
       </c>
       <c r="F30" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G30" t="n">
-        <v>67.7778</v>
+        <v>68.88890000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F31" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>20.6349</v>
+        <v>22.0513</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1348,16 +1348,16 @@
         <v>210</v>
       </c>
       <c r="F32" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G32" t="n">
-        <v>47.1429</v>
+        <v>39.5238</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1377,16 +1377,16 @@
         <v>180</v>
       </c>
       <c r="F33" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G33" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1406,16 +1406,16 @@
         <v>195</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>2.5641</v>
+        <v>1.5385</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1435,16 +1435,16 @@
         <v>210</v>
       </c>
       <c r="F35" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="G35" t="n">
-        <v>48.5714</v>
+        <v>40.9524</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1464,16 +1464,16 @@
         <v>180</v>
       </c>
       <c r="F36" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1522,16 +1522,16 @@
         <v>210</v>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G38" t="n">
-        <v>47.619</v>
+        <v>37.1429</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1551,16 +1551,16 @@
         <v>180</v>
       </c>
       <c r="F39" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G39" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1580,16 +1580,16 @@
         <v>195</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>2.5641</v>
+        <v>1.0256</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1609,16 +1609,16 @@
         <v>210</v>
       </c>
       <c r="F41" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="G41" t="n">
-        <v>48.5714</v>
+        <v>40.9524</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1638,16 +1638,16 @@
         <v>180</v>
       </c>
       <c r="F42" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1667,16 +1667,16 @@
         <v>195</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>1.0256</v>
+        <v>1.5385</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1696,16 +1696,16 @@
         <v>210</v>
       </c>
       <c r="F44" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G44" t="n">
-        <v>49.5238</v>
+        <v>39.0476</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1725,16 +1725,16 @@
         <v>180</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G45" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1754,10 +1754,10 @@
         <v>195</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>1.0256</v>
+        <v>1.5385</v>
       </c>
     </row>
     <row r="47">
@@ -1783,10 +1783,10 @@
         <v>210</v>
       </c>
       <c r="F47" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G47" t="n">
-        <v>60.4762</v>
+        <v>64.28570000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1812,10 +1812,10 @@
         <v>180</v>
       </c>
       <c r="F48" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G48" t="n">
-        <v>99.4444</v>
+        <v>98.88890000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1841,10 +1841,10 @@
         <v>195</v>
       </c>
       <c r="F49" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G49" t="n">
-        <v>92.8205</v>
+        <v>95.38460000000001</v>
       </c>
     </row>
     <row r="50">
@@ -1870,10 +1870,10 @@
         <v>210</v>
       </c>
       <c r="F50" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G50" t="n">
-        <v>59.5238</v>
+        <v>59.0476</v>
       </c>
     </row>
     <row r="51">
@@ -1928,10 +1928,10 @@
         <v>195</v>
       </c>
       <c r="F52" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G52" t="n">
-        <v>96.92310000000001</v>
+        <v>92.8205</v>
       </c>
     </row>
     <row r="53">
@@ -1957,10 +1957,10 @@
         <v>210</v>
       </c>
       <c r="F53" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G53" t="n">
-        <v>58.5714</v>
+        <v>63.8095</v>
       </c>
     </row>
     <row r="54">
@@ -1986,10 +1986,10 @@
         <v>180</v>
       </c>
       <c r="F54" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G54" t="n">
-        <v>98.88890000000001</v>
+        <v>96.66670000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2015,10 +2015,10 @@
         <v>195</v>
       </c>
       <c r="F55" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G55" t="n">
-        <v>93.8462</v>
+        <v>92.8205</v>
       </c>
     </row>
     <row r="56">
@@ -2044,10 +2044,10 @@
         <v>210</v>
       </c>
       <c r="F56" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="G56" t="n">
-        <v>67.619</v>
+        <v>60.4762</v>
       </c>
     </row>
     <row r="57">
@@ -2073,10 +2073,10 @@
         <v>180</v>
       </c>
       <c r="F57" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>99.4444</v>
       </c>
     </row>
     <row r="58">
@@ -2102,10 +2102,10 @@
         <v>195</v>
       </c>
       <c r="F58" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G58" t="n">
-        <v>93.33329999999999</v>
+        <v>94.35899999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2131,10 +2131,10 @@
         <v>210</v>
       </c>
       <c r="F59" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G59" t="n">
-        <v>62.8571</v>
+        <v>58.0952</v>
       </c>
     </row>
     <row r="60">
@@ -2160,10 +2160,10 @@
         <v>180</v>
       </c>
       <c r="F60" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G60" t="n">
-        <v>98.88890000000001</v>
+        <v>98.33329999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2189,10 +2189,10 @@
         <v>195</v>
       </c>
       <c r="F61" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G61" t="n">
-        <v>91.7949</v>
+        <v>93.8462</v>
       </c>
     </row>
     <row r="62">
@@ -2218,10 +2218,10 @@
         <v>210</v>
       </c>
       <c r="F62" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="G62" t="n">
-        <v>92.8571</v>
+        <v>84.7619</v>
       </c>
     </row>
     <row r="63">
@@ -2247,10 +2247,10 @@
         <v>180</v>
       </c>
       <c r="F63" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G63" t="n">
-        <v>61.6667</v>
+        <v>66.66670000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2305,10 +2305,10 @@
         <v>210</v>
       </c>
       <c r="F65" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G65" t="n">
-        <v>90.9524</v>
+        <v>87.619</v>
       </c>
     </row>
     <row r="66">
@@ -2334,10 +2334,10 @@
         <v>180</v>
       </c>
       <c r="F66" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G66" t="n">
-        <v>65.5556</v>
+        <v>63.8889</v>
       </c>
     </row>
     <row r="67">
@@ -2363,10 +2363,10 @@
         <v>195</v>
       </c>
       <c r="F67" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G67" t="n">
-        <v>43.5897</v>
+        <v>47.1795</v>
       </c>
     </row>
     <row r="68">
@@ -2392,10 +2392,10 @@
         <v>210</v>
       </c>
       <c r="F68" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G68" t="n">
-        <v>88.09520000000001</v>
+        <v>86.1905</v>
       </c>
     </row>
     <row r="69">
@@ -2421,10 +2421,10 @@
         <v>180</v>
       </c>
       <c r="F69" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G69" t="n">
-        <v>63.3333</v>
+        <v>63.8889</v>
       </c>
     </row>
     <row r="70">
@@ -2450,10 +2450,10 @@
         <v>195</v>
       </c>
       <c r="F70" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="G70" t="n">
-        <v>36.4103</v>
+        <v>46.1538</v>
       </c>
     </row>
     <row r="71">
@@ -2479,10 +2479,10 @@
         <v>210</v>
       </c>
       <c r="F71" t="n">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G71" t="n">
-        <v>93.8095</v>
+        <v>85.2381</v>
       </c>
     </row>
     <row r="72">
@@ -2537,10 +2537,10 @@
         <v>195</v>
       </c>
       <c r="F73" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G73" t="n">
-        <v>41.5385</v>
+        <v>47.6923</v>
       </c>
     </row>
     <row r="74">
@@ -2566,10 +2566,10 @@
         <v>210</v>
       </c>
       <c r="F74" t="n">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="G74" t="n">
-        <v>91.4286</v>
+        <v>83.33329999999999</v>
       </c>
     </row>
     <row r="75">
@@ -2595,10 +2595,10 @@
         <v>180</v>
       </c>
       <c r="F75" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G75" t="n">
-        <v>63.8889</v>
+        <v>64.4444</v>
       </c>
     </row>
     <row r="76">
@@ -2624,10 +2624,10 @@
         <v>195</v>
       </c>
       <c r="F76" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G76" t="n">
-        <v>41.5385</v>
+        <v>45.641</v>
       </c>
     </row>
     <row r="77">
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="F77" t="n">
         <v>76</v>
       </c>
       <c r="G77" t="n">
-        <v>56.2963</v>
+        <v>45.2381</v>
       </c>
     </row>
     <row r="78">
@@ -2682,10 +2682,10 @@
         <v>180</v>
       </c>
       <c r="F78" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G78" t="n">
-        <v>13.3333</v>
+        <v>11.6667</v>
       </c>
     </row>
     <row r="79">
@@ -2711,10 +2711,10 @@
         <v>195</v>
       </c>
       <c r="F79" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G79" t="n">
-        <v>6.6667</v>
+        <v>7.1795</v>
       </c>
     </row>
     <row r="80">
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="F80" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G80" t="n">
-        <v>57.5758</v>
+        <v>44.0476</v>
       </c>
     </row>
     <row r="81">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F81" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G81" t="n">
-        <v>16.1111</v>
+        <v>18.0791</v>
       </c>
     </row>
     <row r="82">
@@ -2798,10 +2798,10 @@
         <v>195</v>
       </c>
       <c r="F82" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G82" t="n">
-        <v>7.6923</v>
+        <v>5.641</v>
       </c>
     </row>
     <row r="83">
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F83" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="G83" t="n">
-        <v>57.8231</v>
+        <v>36.6013</v>
       </c>
     </row>
     <row r="84">
@@ -2856,10 +2856,10 @@
         <v>180</v>
       </c>
       <c r="F84" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G84" t="n">
-        <v>17.2222</v>
+        <v>11.6667</v>
       </c>
     </row>
     <row r="85">
@@ -2885,10 +2885,10 @@
         <v>195</v>
       </c>
       <c r="F85" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G85" t="n">
-        <v>7.1795</v>
+        <v>5.641</v>
       </c>
     </row>
     <row r="86">
@@ -2911,13 +2911,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F86" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G86" t="n">
-        <v>53.3333</v>
+        <v>47.7987</v>
       </c>
     </row>
     <row r="87">
@@ -2940,13 +2940,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F87" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G87" t="n">
-        <v>16.1111</v>
+        <v>15.2542</v>
       </c>
     </row>
     <row r="88">
@@ -2972,10 +2972,10 @@
         <v>195</v>
       </c>
       <c r="F88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G88" t="n">
-        <v>7.1795</v>
+        <v>7.6923</v>
       </c>
     </row>
     <row r="89">
@@ -2998,13 +2998,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="F89" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G89" t="n">
-        <v>63.7037</v>
+        <v>46.7949</v>
       </c>
     </row>
     <row r="90">
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F90" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G90" t="n">
-        <v>17.2222</v>
+        <v>10.7345</v>
       </c>
     </row>
     <row r="91">
@@ -3059,10 +3059,10 @@
         <v>195</v>
       </c>
       <c r="F91" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G91" t="n">
-        <v>6.6667</v>
+        <v>7.6923</v>
       </c>
     </row>
     <row r="92">
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F92" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G92" t="n">
-        <v>98.5714</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -3146,10 +3146,10 @@
         <v>195</v>
       </c>
       <c r="F94" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G94" t="n">
-        <v>94.87179999999999</v>
+        <v>93.33329999999999</v>
       </c>
     </row>
     <row r="95">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F95" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="G95" t="n">
-        <v>98.09520000000001</v>
+        <v>99.5025</v>
       </c>
     </row>
     <row r="96">
@@ -3233,10 +3233,10 @@
         <v>195</v>
       </c>
       <c r="F97" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G97" t="n">
-        <v>96.92310000000001</v>
+        <v>95.8974</v>
       </c>
     </row>
     <row r="98">
@@ -3259,13 +3259,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F98" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G98" t="n">
-        <v>99.0476</v>
+        <v>99.0196</v>
       </c>
     </row>
     <row r="99">
@@ -3317,13 +3317,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F100" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G100" t="n">
-        <v>97.39579999999999</v>
+        <v>93.8462</v>
       </c>
     </row>
     <row r="101">
@@ -3346,13 +3346,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F101" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G101" t="n">
-        <v>100</v>
+        <v>99.5098</v>
       </c>
     </row>
     <row r="102">
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F104" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G104" t="n">
-        <v>99.51690000000001</v>
+        <v>99.0196</v>
       </c>
     </row>
     <row r="105">
@@ -3523,10 +3523,10 @@
         <v>210</v>
       </c>
       <c r="F107" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G107" t="n">
-        <v>99.0476</v>
+        <v>97.619</v>
       </c>
     </row>
     <row r="108">
@@ -3552,10 +3552,10 @@
         <v>180</v>
       </c>
       <c r="F108" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G108" t="n">
-        <v>91.66670000000001</v>
+        <v>92.2222</v>
       </c>
     </row>
     <row r="109">
@@ -3581,10 +3581,10 @@
         <v>195</v>
       </c>
       <c r="F109" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G109" t="n">
-        <v>61.5385</v>
+        <v>67.6923</v>
       </c>
     </row>
     <row r="110">
@@ -3610,10 +3610,10 @@
         <v>210</v>
       </c>
       <c r="F110" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G110" t="n">
-        <v>97.619</v>
+        <v>97.1429</v>
       </c>
     </row>
     <row r="111">
@@ -3639,10 +3639,10 @@
         <v>180</v>
       </c>
       <c r="F111" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G111" t="n">
-        <v>92.7778</v>
+        <v>92.2222</v>
       </c>
     </row>
     <row r="112">
@@ -3668,10 +3668,10 @@
         <v>195</v>
       </c>
       <c r="F112" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G112" t="n">
-        <v>62.5641</v>
+        <v>65.64100000000001</v>
       </c>
     </row>
     <row r="113">
@@ -3697,10 +3697,10 @@
         <v>210</v>
       </c>
       <c r="F113" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G113" t="n">
-        <v>99.52379999999999</v>
+        <v>95.2381</v>
       </c>
     </row>
     <row r="114">
@@ -3726,10 +3726,10 @@
         <v>180</v>
       </c>
       <c r="F114" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G114" t="n">
-        <v>93.33329999999999</v>
+        <v>92.2222</v>
       </c>
     </row>
     <row r="115">
@@ -3755,10 +3755,10 @@
         <v>195</v>
       </c>
       <c r="F115" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G115" t="n">
-        <v>61.0256</v>
+        <v>65.12820000000001</v>
       </c>
     </row>
     <row r="116">
@@ -3784,10 +3784,10 @@
         <v>210</v>
       </c>
       <c r="F116" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G116" t="n">
-        <v>98.5714</v>
+        <v>97.1429</v>
       </c>
     </row>
     <row r="117">
@@ -3813,10 +3813,10 @@
         <v>180</v>
       </c>
       <c r="F117" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G117" t="n">
-        <v>93.33329999999999</v>
+        <v>94.4444</v>
       </c>
     </row>
     <row r="118">
@@ -3842,10 +3842,10 @@
         <v>195</v>
       </c>
       <c r="F118" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G118" t="n">
-        <v>65.64100000000001</v>
+        <v>63.5897</v>
       </c>
     </row>
     <row r="119">
@@ -3871,10 +3871,10 @@
         <v>210</v>
       </c>
       <c r="F119" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G119" t="n">
-        <v>99.52379999999999</v>
+        <v>97.1429</v>
       </c>
     </row>
     <row r="120">
@@ -3900,10 +3900,10 @@
         <v>180</v>
       </c>
       <c r="F120" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G120" t="n">
-        <v>92.7778</v>
+        <v>93.88890000000001</v>
       </c>
     </row>
     <row r="121">
@@ -3929,10 +3929,10 @@
         <v>195</v>
       </c>
       <c r="F121" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G121" t="n">
-        <v>58.9744</v>
+        <v>63.5897</v>
       </c>
     </row>
     <row r="122">
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F122" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G122" t="n">
-        <v>48.3092</v>
+        <v>45.7143</v>
       </c>
     </row>
     <row r="123">
@@ -3987,10 +3987,10 @@
         <v>180</v>
       </c>
       <c r="F123" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G123" t="n">
-        <v>11.1111</v>
+        <v>6.6667</v>
       </c>
     </row>
     <row r="124">
@@ -4016,10 +4016,10 @@
         <v>195</v>
       </c>
       <c r="F124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G124" t="n">
-        <v>6.1538</v>
+        <v>5.641</v>
       </c>
     </row>
     <row r="125">
@@ -4045,10 +4045,10 @@
         <v>210</v>
       </c>
       <c r="F125" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="G125" t="n">
-        <v>50</v>
+        <v>44.2857</v>
       </c>
     </row>
     <row r="126">
@@ -4074,10 +4074,10 @@
         <v>180</v>
       </c>
       <c r="F126" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G126" t="n">
-        <v>10.5556</v>
+        <v>6.1111</v>
       </c>
     </row>
     <row r="127">
@@ -4103,10 +4103,10 @@
         <v>195</v>
       </c>
       <c r="F127" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G127" t="n">
-        <v>7.1795</v>
+        <v>5.641</v>
       </c>
     </row>
     <row r="128">
@@ -4132,10 +4132,10 @@
         <v>210</v>
       </c>
       <c r="F128" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G128" t="n">
-        <v>45.7143</v>
+        <v>48.0952</v>
       </c>
     </row>
     <row r="129">
@@ -4161,10 +4161,10 @@
         <v>180</v>
       </c>
       <c r="F129" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G129" t="n">
-        <v>11.1111</v>
+        <v>7.7778</v>
       </c>
     </row>
     <row r="130">
@@ -4190,10 +4190,10 @@
         <v>195</v>
       </c>
       <c r="F130" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G130" t="n">
-        <v>6.6667</v>
+        <v>4.6154</v>
       </c>
     </row>
     <row r="131">
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F131" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G131" t="n">
-        <v>49.2754</v>
+        <v>46.6667</v>
       </c>
     </row>
     <row r="132">
@@ -4248,10 +4248,10 @@
         <v>180</v>
       </c>
       <c r="F132" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G132" t="n">
-        <v>11.6667</v>
+        <v>10.5556</v>
       </c>
     </row>
     <row r="133">
@@ -4277,10 +4277,10 @@
         <v>195</v>
       </c>
       <c r="F133" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G133" t="n">
-        <v>4.1026</v>
+        <v>5.641</v>
       </c>
     </row>
     <row r="134">
@@ -4306,10 +4306,10 @@
         <v>210</v>
       </c>
       <c r="F134" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G134" t="n">
-        <v>47.1429</v>
+        <v>43.8095</v>
       </c>
     </row>
     <row r="135">
@@ -4335,10 +4335,10 @@
         <v>180</v>
       </c>
       <c r="F135" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G135" t="n">
-        <v>11.6667</v>
+        <v>6.1111</v>
       </c>
     </row>
     <row r="136">
@@ -4364,16 +4364,16 @@
         <v>195</v>
       </c>
       <c r="F136" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G136" t="n">
-        <v>6.6667</v>
+        <v>5.1282</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4393,16 +4393,16 @@
         <v>210</v>
       </c>
       <c r="F137" t="n">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="G137" t="n">
-        <v>57.619</v>
+        <v>33.3333</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4422,16 +4422,16 @@
         <v>180</v>
       </c>
       <c r="F138" t="n">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="G138" t="n">
-        <v>77.7778</v>
+        <v>98.33329999999999</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4448,19 +4448,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F139" t="n">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="G139" t="n">
-        <v>56.6138</v>
+        <v>25.1282</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4480,16 +4480,16 @@
         <v>210</v>
       </c>
       <c r="F140" t="n">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="G140" t="n">
-        <v>50.9524</v>
+        <v>33.8095</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4506,19 +4506,19 @@
         </is>
       </c>
       <c r="E141" t="n">
+        <v>180</v>
+      </c>
+      <c r="F141" t="n">
         <v>177</v>
       </c>
-      <c r="F141" t="n">
-        <v>133</v>
-      </c>
       <c r="G141" t="n">
-        <v>75.1412</v>
+        <v>98.33329999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4538,16 +4538,16 @@
         <v>195</v>
       </c>
       <c r="F142" t="n">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="G142" t="n">
-        <v>59.4872</v>
+        <v>27.6923</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4564,19 +4564,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F143" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="G143" t="n">
-        <v>51.2077</v>
+        <v>33.8095</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4593,19 +4593,19 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F144" t="n">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="G144" t="n">
-        <v>84.1808</v>
+        <v>98.88890000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4622,19 +4622,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F145" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="G145" t="n">
-        <v>60.4167</v>
+        <v>27.1795</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4654,16 +4654,16 @@
         <v>210</v>
       </c>
       <c r="F146" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="G146" t="n">
-        <v>63.3333</v>
+        <v>32.8571</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4680,19 +4680,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F147" t="n">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="G147" t="n">
-        <v>76.27119999999999</v>
+        <v>99.4444</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4712,16 +4712,16 @@
         <v>195</v>
       </c>
       <c r="F148" t="n">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="G148" t="n">
-        <v>61.0256</v>
+        <v>26.6667</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4741,16 +4741,16 @@
         <v>210</v>
       </c>
       <c r="F149" t="n">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="G149" t="n">
-        <v>54.2857</v>
+        <v>35.7143</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4770,16 +4770,16 @@
         <v>180</v>
       </c>
       <c r="F150" t="n">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="G150" t="n">
-        <v>73.33329999999999</v>
+        <v>99.4444</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4799,16 +4799,16 @@
         <v>195</v>
       </c>
       <c r="F151" t="n">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="G151" t="n">
-        <v>55.8974</v>
+        <v>22.5641</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4828,16 +4828,16 @@
         <v>210</v>
       </c>
       <c r="F152" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G152" t="n">
-        <v>94.7619</v>
+        <v>92.8571</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4883,19 +4883,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F154" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="G154" t="n">
-        <v>27.6923</v>
+        <v>40.1042</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4915,16 +4915,16 @@
         <v>210</v>
       </c>
       <c r="F155" t="n">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G155" t="n">
-        <v>95.71429999999999</v>
+        <v>91.4286</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4944,16 +4944,16 @@
         <v>180</v>
       </c>
       <c r="F156" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G156" t="n">
-        <v>65.5556</v>
+        <v>67.7778</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4973,16 +4973,16 @@
         <v>195</v>
       </c>
       <c r="F157" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G157" t="n">
-        <v>30.2564</v>
+        <v>38.9744</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5002,16 +5002,16 @@
         <v>210</v>
       </c>
       <c r="F158" t="n">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G158" t="n">
-        <v>95.71429999999999</v>
+        <v>92.8571</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5031,16 +5031,16 @@
         <v>180</v>
       </c>
       <c r="F159" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="G159" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5060,16 +5060,16 @@
         <v>195</v>
       </c>
       <c r="F160" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="G160" t="n">
-        <v>26.6667</v>
+        <v>39.4872</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5089,16 +5089,16 @@
         <v>210</v>
       </c>
       <c r="F161" t="n">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G161" t="n">
-        <v>94.7619</v>
+        <v>91.90479999999999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5118,16 +5118,16 @@
         <v>180</v>
       </c>
       <c r="F162" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G162" t="n">
-        <v>67.2222</v>
+        <v>72.2222</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5147,16 +5147,16 @@
         <v>195</v>
       </c>
       <c r="F163" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="G163" t="n">
-        <v>27.6923</v>
+        <v>38.4615</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5176,16 +5176,16 @@
         <v>210</v>
       </c>
       <c r="F164" t="n">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="G164" t="n">
-        <v>97.619</v>
+        <v>91.90479999999999</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5205,16 +5205,16 @@
         <v>180</v>
       </c>
       <c r="F165" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G165" t="n">
-        <v>62.7778</v>
+        <v>65</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5234,16 +5234,16 @@
         <v>195</v>
       </c>
       <c r="F166" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="G166" t="n">
-        <v>28.7179</v>
+        <v>41.0256</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5263,16 +5263,16 @@
         <v>210</v>
       </c>
       <c r="F167" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G167" t="n">
-        <v>43.3333</v>
+        <v>43.8095</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5292,16 +5292,16 @@
         <v>180</v>
       </c>
       <c r="F168" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G168" t="n">
-        <v>14.4444</v>
+        <v>13.8889</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5321,16 +5321,16 @@
         <v>195</v>
       </c>
       <c r="F169" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G169" t="n">
-        <v>12.8205</v>
+        <v>6.6667</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5350,16 +5350,16 @@
         <v>207</v>
       </c>
       <c r="F170" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G170" t="n">
-        <v>52.1739</v>
+        <v>51.2077</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5379,16 +5379,16 @@
         <v>180</v>
       </c>
       <c r="F171" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G171" t="n">
-        <v>14.4444</v>
+        <v>12.7778</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5408,16 +5408,16 @@
         <v>195</v>
       </c>
       <c r="F172" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G172" t="n">
-        <v>6.6667</v>
+        <v>6.1538</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5434,19 +5434,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F173" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G173" t="n">
-        <v>45.2381</v>
+        <v>45.4106</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5466,16 +5466,16 @@
         <v>180</v>
       </c>
       <c r="F174" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G174" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5495,16 +5495,16 @@
         <v>195</v>
       </c>
       <c r="F175" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G175" t="n">
-        <v>8.2051</v>
+        <v>7.1795</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>210</v>
       </c>
       <c r="F176" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G176" t="n">
-        <v>45.7143</v>
+        <v>43.8095</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5553,16 +5553,16 @@
         <v>180</v>
       </c>
       <c r="F177" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G177" t="n">
-        <v>16.6667</v>
+        <v>12.7778</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5582,16 +5582,16 @@
         <v>195</v>
       </c>
       <c r="F178" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G178" t="n">
-        <v>6.1538</v>
+        <v>6.6667</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5611,16 +5611,16 @@
         <v>210</v>
       </c>
       <c r="F179" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="G179" t="n">
-        <v>50</v>
+        <v>43.8095</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5640,16 +5640,16 @@
         <v>180</v>
       </c>
       <c r="F180" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G180" t="n">
-        <v>14.4444</v>
+        <v>12.2222</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5669,10 +5669,10 @@
         <v>195</v>
       </c>
       <c r="F181" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G181" t="n">
-        <v>6.1538</v>
+        <v>7.1795</v>
       </c>
     </row>
   </sheetData>
@@ -5734,7 +5734,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5751,22 +5751,22 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>76.5714</v>
+        <v>43.0476</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1402</v>
+        <v>2.092</v>
       </c>
       <c r="G2" t="n">
-        <v>73.8095</v>
+        <v>39.5238</v>
       </c>
       <c r="H2" t="n">
-        <v>78.5714</v>
+        <v>44.7619</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5783,22 +5783,22 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>96.5556</v>
+        <v>66.4444</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3263</v>
+        <v>4.0938</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>61.1111</v>
       </c>
       <c r="H3" t="n">
-        <v>98.33329999999999</v>
+        <v>71.11109999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5815,22 +5815,22 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>15.0769</v>
+        <v>6.9743</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0384</v>
+        <v>0.8581</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3333</v>
+        <v>6.1538</v>
       </c>
       <c r="H4" t="n">
-        <v>17.9487</v>
+        <v>8.2051</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5847,22 +5847,22 @@
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>99.0393</v>
+        <v>89.8095</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6808</v>
+        <v>2.7889</v>
       </c>
       <c r="G5" t="n">
-        <v>98.55070000000001</v>
+        <v>85.71429999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>93.33329999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5882,19 +5882,19 @@
         <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8426</v>
+        <v>1.4487</v>
       </c>
       <c r="G6" t="n">
-        <v>66.11109999999999</v>
+        <v>65</v>
       </c>
       <c r="H6" t="n">
-        <v>67.7778</v>
+        <v>68.88890000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5911,22 +5911,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>21.3794</v>
+        <v>21.9487</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7526</v>
+        <v>0.9174</v>
       </c>
       <c r="G7" t="n">
-        <v>20.6349</v>
+        <v>21.0256</v>
       </c>
       <c r="H7" t="n">
-        <v>22.3958</v>
+        <v>23.0769</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5943,22 +5943,22 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>48.2857</v>
+        <v>39.5238</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9283</v>
+        <v>1.5793</v>
       </c>
       <c r="G8" t="n">
-        <v>47.1429</v>
+        <v>37.1429</v>
       </c>
       <c r="H8" t="n">
-        <v>49.5238</v>
+        <v>40.9524</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5975,22 +5975,22 @@
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
       <c r="H9" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6007,10 +6007,10 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9487</v>
+        <v>1.641</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8427</v>
+        <v>0.5618</v>
       </c>
       <c r="G10" t="n">
         <v>1.0256</v>
@@ -6039,16 +6039,16 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>61.8095</v>
+        <v>61.1428</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6172</v>
+        <v>2.7889</v>
       </c>
       <c r="G11" t="n">
-        <v>58.5714</v>
+        <v>58.0952</v>
       </c>
       <c r="H11" t="n">
-        <v>67.619</v>
+        <v>64.28570000000001</v>
       </c>
     </row>
     <row r="12">
@@ -6071,16 +6071,16 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>99.2222</v>
+        <v>98.4444</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4969</v>
+        <v>1.0686</v>
       </c>
       <c r="G12" t="n">
-        <v>98.88890000000001</v>
+        <v>96.66670000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>100</v>
+        <v>99.4444</v>
       </c>
     </row>
     <row r="13">
@@ -6103,16 +6103,16 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>93.7436</v>
+        <v>93.8462</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9325</v>
+        <v>1.0879</v>
       </c>
       <c r="G13" t="n">
-        <v>91.7949</v>
+        <v>92.8205</v>
       </c>
       <c r="H13" t="n">
-        <v>96.92310000000001</v>
+        <v>95.38460000000001</v>
       </c>
     </row>
     <row r="14">
@@ -6135,16 +6135,16 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>91.4286</v>
+        <v>85.4286</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1822</v>
+        <v>1.6007</v>
       </c>
       <c r="G14" t="n">
-        <v>88.09520000000001</v>
+        <v>83.33329999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>93.8095</v>
+        <v>87.619</v>
       </c>
     </row>
     <row r="15">
@@ -6167,16 +6167,16 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>63</v>
+        <v>63.8889</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9484</v>
+        <v>2.1872</v>
       </c>
       <c r="G15" t="n">
         <v>60.5556</v>
       </c>
       <c r="H15" t="n">
-        <v>65.5556</v>
+        <v>66.66670000000001</v>
       </c>
     </row>
     <row r="16">
@@ -6199,16 +6199,16 @@
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>41.2308</v>
+        <v>45.9487</v>
       </c>
       <c r="F16" t="n">
-        <v>2.846</v>
+        <v>1.7985</v>
       </c>
       <c r="G16" t="n">
-        <v>36.4103</v>
+        <v>43.0769</v>
       </c>
       <c r="H16" t="n">
-        <v>43.5897</v>
+        <v>47.6923</v>
       </c>
     </row>
     <row r="17">
@@ -6231,16 +6231,16 @@
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>57.7464</v>
+        <v>44.0961</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7783</v>
+        <v>4.4292</v>
       </c>
       <c r="G17" t="n">
-        <v>53.3333</v>
+        <v>36.6013</v>
       </c>
       <c r="H17" t="n">
-        <v>63.7037</v>
+        <v>47.7987</v>
       </c>
     </row>
     <row r="18">
@@ -6263,16 +6263,16 @@
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>13.4802</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5909</v>
+        <v>3.0989</v>
       </c>
       <c r="G18" t="n">
-        <v>13.3333</v>
+        <v>10.7345</v>
       </c>
       <c r="H18" t="n">
-        <v>17.2222</v>
+        <v>18.0791</v>
       </c>
     </row>
     <row r="19">
@@ -6295,13 +6295,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>7.0769</v>
+        <v>6.7692</v>
       </c>
       <c r="F19" t="n">
-        <v>0.429</v>
+        <v>1.051</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6667</v>
+        <v>5.641</v>
       </c>
       <c r="H19" t="n">
         <v>7.6923</v>
@@ -6327,13 +6327,13 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>99.0462</v>
+        <v>99.41030000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7519</v>
+        <v>0.4097</v>
       </c>
       <c r="G20" t="n">
-        <v>98.09520000000001</v>
+        <v>99.0196</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -6391,16 +6391,16 @@
         <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>95.5817</v>
+        <v>94.35899999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5092</v>
+        <v>1.0256</v>
       </c>
       <c r="G22" t="n">
-        <v>93.8462</v>
+        <v>93.33329999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>97.39579999999999</v>
+        <v>95.8974</v>
       </c>
     </row>
     <row r="23">
@@ -6423,16 +6423,16 @@
         <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>98.8571</v>
+        <v>96.85720000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7968</v>
+        <v>0.9283</v>
       </c>
       <c r="G23" t="n">
+        <v>95.2381</v>
+      </c>
+      <c r="H23" t="n">
         <v>97.619</v>
-      </c>
-      <c r="H23" t="n">
-        <v>99.52379999999999</v>
       </c>
     </row>
     <row r="24">
@@ -6455,16 +6455,16 @@
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>92.7778</v>
+        <v>93</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6804</v>
+        <v>1.083</v>
       </c>
       <c r="G24" t="n">
-        <v>91.66670000000001</v>
+        <v>92.2222</v>
       </c>
       <c r="H24" t="n">
-        <v>93.33329999999999</v>
+        <v>94.4444</v>
       </c>
     </row>
     <row r="25">
@@ -6487,16 +6487,16 @@
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>61.9487</v>
+        <v>65.12820000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4433</v>
+        <v>1.7008</v>
       </c>
       <c r="G25" t="n">
-        <v>58.9744</v>
+        <v>63.5897</v>
       </c>
       <c r="H25" t="n">
-        <v>65.64100000000001</v>
+        <v>67.6923</v>
       </c>
     </row>
     <row r="26">
@@ -6519,16 +6519,16 @@
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>48.0884</v>
+        <v>45.7143</v>
       </c>
       <c r="F26" t="n">
-        <v>1.706</v>
+        <v>1.7496</v>
       </c>
       <c r="G26" t="n">
-        <v>45.7143</v>
+        <v>43.8095</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>48.0952</v>
       </c>
     </row>
     <row r="27">
@@ -6551,16 +6551,16 @@
         <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2222</v>
+        <v>7.4445</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4648</v>
+        <v>1.8675</v>
       </c>
       <c r="G27" t="n">
+        <v>6.1111</v>
+      </c>
+      <c r="H27" t="n">
         <v>10.5556</v>
-      </c>
-      <c r="H27" t="n">
-        <v>11.6667</v>
       </c>
     </row>
     <row r="28">
@@ -6583,22 +6583,22 @@
         <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>6.1539</v>
+        <v>5.3333</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2027</v>
+        <v>0.4587</v>
       </c>
       <c r="G28" t="n">
-        <v>4.1026</v>
+        <v>4.6154</v>
       </c>
       <c r="H28" t="n">
-        <v>7.1795</v>
+        <v>5.641</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6615,22 +6615,22 @@
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>55.4796</v>
+        <v>33.9047</v>
       </c>
       <c r="F29" t="n">
-        <v>5.1582</v>
+        <v>1.0859</v>
       </c>
       <c r="G29" t="n">
-        <v>50.9524</v>
+        <v>32.8571</v>
       </c>
       <c r="H29" t="n">
-        <v>63.3333</v>
+        <v>35.7143</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6647,22 +6647,22 @@
         <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>77.3409</v>
+        <v>98.88890000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>4.1539</v>
+        <v>0.5556</v>
       </c>
       <c r="G30" t="n">
-        <v>73.33329999999999</v>
+        <v>98.33329999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>84.1808</v>
+        <v>99.4444</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6679,22 +6679,22 @@
         <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>58.6881</v>
+        <v>25.8462</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3012</v>
+        <v>2.0704</v>
       </c>
       <c r="G31" t="n">
-        <v>55.8974</v>
+        <v>22.5641</v>
       </c>
       <c r="H31" t="n">
-        <v>61.0256</v>
+        <v>27.6923</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6711,22 +6711,22 @@
         <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>95.71429999999999</v>
+        <v>92.1905</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1664</v>
+        <v>0.6388</v>
       </c>
       <c r="G32" t="n">
-        <v>94.7619</v>
+        <v>91.4286</v>
       </c>
       <c r="H32" t="n">
-        <v>97.619</v>
+        <v>92.8571</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6743,22 +6743,22 @@
         <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>66.5556</v>
+        <v>67.4444</v>
       </c>
       <c r="F33" t="n">
-        <v>2.6469</v>
+        <v>2.9554</v>
       </c>
       <c r="G33" t="n">
-        <v>62.7778</v>
+        <v>65</v>
       </c>
       <c r="H33" t="n">
-        <v>70</v>
+        <v>72.2222</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6775,22 +6775,22 @@
         <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>28.2051</v>
+        <v>39.6106</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3568</v>
+        <v>0.9983</v>
       </c>
       <c r="G34" t="n">
-        <v>26.6667</v>
+        <v>38.4615</v>
       </c>
       <c r="H34" t="n">
-        <v>30.2564</v>
+        <v>41.0256</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6807,22 +6807,22 @@
         <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>47.2919</v>
+        <v>45.6094</v>
       </c>
       <c r="F35" t="n">
-        <v>3.6587</v>
+        <v>3.2054</v>
       </c>
       <c r="G35" t="n">
-        <v>43.3333</v>
+        <v>43.8095</v>
       </c>
       <c r="H35" t="n">
-        <v>52.1739</v>
+        <v>51.2077</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6839,22 +6839,22 @@
         <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>14.8889</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9938</v>
+        <v>0.6334</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4444</v>
+        <v>12.2222</v>
       </c>
       <c r="H36" t="n">
-        <v>16.6667</v>
+        <v>13.8889</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6871,16 +6871,16 @@
         <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>6.7692</v>
       </c>
       <c r="F37" t="n">
-        <v>2.8228</v>
+        <v>0.4291</v>
       </c>
       <c r="G37" t="n">
         <v>6.1538</v>
       </c>
       <c r="H37" t="n">
-        <v>12.8205</v>
+        <v>7.1795</v>
       </c>
     </row>
   </sheetData>
@@ -6942,7 +6942,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6959,22 +6959,22 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>48.2857</v>
+        <v>39.5238</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9283</v>
+        <v>1.5793</v>
       </c>
       <c r="G2" t="n">
-        <v>47.1429</v>
+        <v>37.1429</v>
       </c>
       <c r="H2" t="n">
-        <v>49.5238</v>
+        <v>40.9524</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6991,22 +6991,22 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
       <c r="H3" t="n">
-        <v>14.4444</v>
+        <v>13.3333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Gemini 3.8 Flash</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7023,10 +7023,10 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9487</v>
+        <v>1.641</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8427</v>
+        <v>0.5618</v>
       </c>
       <c r="G4" t="n">
         <v>1.0256</v>
@@ -7055,16 +7055,16 @@
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>57.7464</v>
+        <v>44.0961</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7783</v>
+        <v>4.4292</v>
       </c>
       <c r="G5" t="n">
-        <v>53.3333</v>
+        <v>36.6013</v>
       </c>
       <c r="H5" t="n">
-        <v>63.7037</v>
+        <v>47.7987</v>
       </c>
     </row>
     <row r="6">
@@ -7087,16 +7087,16 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>13.4802</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5909</v>
+        <v>3.0989</v>
       </c>
       <c r="G6" t="n">
-        <v>13.3333</v>
+        <v>10.7345</v>
       </c>
       <c r="H6" t="n">
-        <v>17.2222</v>
+        <v>18.0791</v>
       </c>
     </row>
     <row r="7">
@@ -7119,13 +7119,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>7.0769</v>
+        <v>6.7692</v>
       </c>
       <c r="F7" t="n">
-        <v>0.429</v>
+        <v>1.051</v>
       </c>
       <c r="G7" t="n">
-        <v>6.6667</v>
+        <v>5.641</v>
       </c>
       <c r="H7" t="n">
         <v>7.6923</v>
@@ -7151,16 +7151,16 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>48.0884</v>
+        <v>45.7143</v>
       </c>
       <c r="F8" t="n">
-        <v>1.706</v>
+        <v>1.7496</v>
       </c>
       <c r="G8" t="n">
-        <v>45.7143</v>
+        <v>43.8095</v>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>48.0952</v>
       </c>
     </row>
     <row r="9">
@@ -7183,16 +7183,16 @@
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>11.2222</v>
+        <v>7.4445</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4648</v>
+        <v>1.8675</v>
       </c>
       <c r="G9" t="n">
+        <v>6.1111</v>
+      </c>
+      <c r="H9" t="n">
         <v>10.5556</v>
-      </c>
-      <c r="H9" t="n">
-        <v>11.6667</v>
       </c>
     </row>
     <row r="10">
@@ -7215,22 +7215,22 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1539</v>
+        <v>5.3333</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2027</v>
+        <v>0.4587</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1026</v>
+        <v>4.6154</v>
       </c>
       <c r="H10" t="n">
-        <v>7.1795</v>
+        <v>5.641</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7247,22 +7247,22 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>47.2919</v>
+        <v>45.6094</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6587</v>
+        <v>3.2054</v>
       </c>
       <c r="G11" t="n">
-        <v>43.3333</v>
+        <v>43.8095</v>
       </c>
       <c r="H11" t="n">
-        <v>52.1739</v>
+        <v>51.2077</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7279,22 +7279,22 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>14.8889</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9938</v>
+        <v>0.6334</v>
       </c>
       <c r="G12" t="n">
-        <v>14.4444</v>
+        <v>12.2222</v>
       </c>
       <c r="H12" t="n">
-        <v>16.6667</v>
+        <v>13.8889</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7311,16 +7311,16 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>6.7692</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8228</v>
+        <v>0.4291</v>
       </c>
       <c r="G13" t="n">
         <v>6.1538</v>
       </c>
       <c r="H13" t="n">
-        <v>12.8205</v>
+        <v>7.1795</v>
       </c>
     </row>
   </sheetData>
